--- a/p6_deployment/data/france/predicciones.xlsx
+++ b/p6_deployment/data/france/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,70 +520,40 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>dif_prob_mod_bm</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>result_to_bet</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>dif_prob_result_to_bet</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>prob_result_to_bet</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>odd_to_bet</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>result_to_bet</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_prob_result_to_bet</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>prob_result_to_bet</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>odd_to_bet</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -639,46 +609,40 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1824824230231364</v>
+        <v>0.1834363301798725</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2703557467926924</v>
+        <v>0.2961208267126468</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5471618301841712</v>
+        <v>0.5204428431074806</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>-0.03717797473638562</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.03717797473638562</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5204428431074806</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
       <c r="Y2" t="n">
-        <v>-0.010458987659695</v>
+        <v>41.63542744859845</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.010458987659695</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.5471618301841712</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>43.7729464147337</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>43.7729464147337</v>
+        <v>41.63542744859845</v>
       </c>
     </row>
     <row r="3">
@@ -731,46 +695,40 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.571466713250923</v>
+        <v>0.5925367048167887</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2286600195218835</v>
+        <v>0.2313466117095582</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1998732672271934</v>
+        <v>0.1761166834736529</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-0.1176561771136446</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1176561771136446</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4074632951832113</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.259259259259259</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
       <c r="Y3" t="n">
-        <v>-0.1387261686795103</v>
+        <v>32.5970636146569</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.1387261686795103</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.428533286749077</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.259259259259259</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>34.28266293992615</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>34.28266293992615</v>
+        <v>32.5970636146569</v>
       </c>
     </row>
     <row r="4">
@@ -823,46 +781,40 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4818938256214655</v>
+        <v>0.4255422506051418</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2817080386414592</v>
+        <v>0.283665625099262</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2363981357370753</v>
+        <v>0.290792124295596</v>
       </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>-0.2079298906652903</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.2079298906652903</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5744577493948582</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.55789224952741</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
       <c r="Y4" t="n">
-        <v>-0.1515783156489665</v>
+        <v>45.95661995158865</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.1515783156489665</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.5181061743785345</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.55789224952741</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>41.44849395028275</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>41.44849395028275</v>
+        <v>45.95661995158865</v>
       </c>
     </row>
     <row r="5">
@@ -915,46 +867,40 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.492740122718396</v>
+        <v>0.4923772643437557</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2970389034982143</v>
+        <v>0.2944436302719333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2102209737833899</v>
+        <v>0.2131791053843112</v>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>-0.09251578378458664</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.09251578378458664</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5076227356562444</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.282608695652174</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
-        <v>-0.09215292540994635</v>
+        <v>40.60981885249955</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.09215292540994635</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.507259877281604</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.282608695652174</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>40.58079018252833</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>40.58079018252833</v>
+        <v>40.60981885249955</v>
       </c>
     </row>
     <row r="6">
@@ -1007,46 +953,40 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6581697888277576</v>
+        <v>0.6458454848983202</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2342002373094837</v>
+        <v>0.24062082636494</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1076299738627585</v>
+        <v>0.1135336887367399</v>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-0.07645719431963771</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.07645719431963771</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3541545151016798</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.38135593220339</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
       <c r="Y6" t="n">
-        <v>-0.06413289039020031</v>
+        <v>28.33236120813439</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.06413289039020031</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.3418302111722424</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.38135593220339</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>27.34641689377939</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>27.34641689377939</v>
+        <v>28.33236120813439</v>
       </c>
     </row>
     <row r="7">
@@ -1099,46 +1039,40 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6117514889343022</v>
+        <v>0.6573982211643515</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07264063914342561</v>
+        <v>0.06372951367054189</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3156078719222722</v>
+        <v>0.2788722651651065</v>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0.4573209712609139</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4573209712609139</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6573982211643515</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
       <c r="Y7" t="n">
-        <v>0.4116742390308645</v>
+        <v>52.59185769314812</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.4116742390308645</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.6117514889343022</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>48.94011911474418</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>48.94011911474418</v>
+        <v>52.59185769314812</v>
       </c>
     </row>
     <row r="8">
@@ -1191,46 +1125,40 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6257472714537949</v>
+        <v>0.6156360722259568</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2449677452611624</v>
+        <v>0.251132880122871</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1292849832850425</v>
+        <v>0.133231047651172</v>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>-0.02330444822013977</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.02330444822013977</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6156360722259568</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
       <c r="Y8" t="n">
-        <v>-0.01319324899230168</v>
+        <v>49.25088577807655</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.01319324899230168</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.6257472714537949</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>50.0597817163036</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>50.0597817163036</v>
+        <v>49.25088577807655</v>
       </c>
     </row>
     <row r="9">
@@ -1283,60 +1211,42 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2711750760571567</v>
+        <v>0.234329403268049</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3422199070588398</v>
+        <v>0.3367897036040899</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3866050168840033</v>
+        <v>0.428880893127861</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>25.53194444444444</v>
+        <v>0.02781137441128351</v>
       </c>
       <c r="T9" t="n">
-        <v>182.5777777777778</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.216666666666667</v>
+        <v>0.02781137441128351</v>
       </c>
       <c r="V9" t="n">
-        <v>74.47499999999999</v>
+        <v>0.428880893127861</v>
       </c>
       <c r="W9" t="n">
-        <v>7554409.722222222</v>
-      </c>
-      <c r="X9" t="n">
-        <v>78.77500000000001</v>
+        <v>2.38</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
       </c>
       <c r="Y9" t="n">
-        <v>-0.01446450183257425</v>
+        <v>34.31047145022888</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.01446450183257425</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.3866050168840033</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>30.92840135072026</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>30.92840135072026</v>
+        <v>34.31047145022888</v>
       </c>
     </row>
     <row r="10">
@@ -1389,46 +1299,40 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2423008501792831</v>
+        <v>0.2634201695928</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2985269529080498</v>
+        <v>0.3126713810085349</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4591721969126671</v>
+        <v>0.4239084493986652</v>
       </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0.00820406140790314</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.00820406140790314</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4239084493986652</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
       <c r="Y10" t="n">
-        <v>0.04346780892190505</v>
+        <v>33.91267595189322</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.04346780892190505</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.4591721969126671</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="AE10" t="n">
-        <v>36.73377575301337</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>36.73377575301337</v>
+        <v>33.91267595189322</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/predicciones.xlsx
+++ b/p6_deployment/data/france/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>88K4TzrO</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,84 +594,96 @@
       <c r="F2" t="n">
         <v>551</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.75</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>5.25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1895910780669145</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2527881040892193</v>
+        <v>1.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5576208178438662</v>
+        <v>0.1789903110657828</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05490196078431375</v>
+        <v>0.2409484956654768</v>
       </c>
       <c r="N2" t="n">
+        <v>0.5800611932687404</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06417039750373088</v>
+      </c>
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.1834363301798725</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2961208267126468</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0.5204428431074806</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0.1746666286593137</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1541996299822143</v>
+      </c>
       <c r="S2" t="n">
-        <v>-0.03717797473638562</v>
+        <v>0.6711337413584719</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.09107254808973153</v>
+      </c>
+      <c r="V2" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
-        <v>-0.03717797473638562</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.5204428431074806</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>0.09107254808973153</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6711337413584719</v>
       </c>
       <c r="Y2" t="n">
-        <v>41.63542744859845</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>41.63542744859845</v>
+        <v>1.62</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>53.69069930867775</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>53.69069930867775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ek4VdDB</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -670,84 +692,96 @@
       <c r="F3" t="n">
         <v>551</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.5</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7101928819304333</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1717375514486321</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1180695666209345</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05869788106630214</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="N3" t="n">
+        <v>0.4302959501557632</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05635540929658589</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2311760468323598</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.188741386262389</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5800825669052508</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.5925367048167887</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.2313466117095582</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.1761166834736529</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>-0.1176561771136446</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1</v>
-      </c>
       <c r="U3" t="n">
-        <v>0.1176561771136446</v>
+        <v>0.1497866167494877</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4074632951832113</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>3.259259259259259</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
+        <v>0.1497866167494877</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5800825669052508</v>
       </c>
       <c r="Y3" t="n">
-        <v>32.5970636146569</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>32.5970636146569</v>
+        <v>2.2</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>46.40660535242007</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>46.40660535242007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>naJ8SfcU</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -756,84 +790,96 @@
       <c r="F4" t="n">
         <v>551</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.33</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6334721412704321</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2165216556767297</v>
+        <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1500062030528383</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06662255789276572</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="N4" t="n">
+        <v>0.3437815975733064</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05775401069518704</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3528486016858882</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2490421143480716</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3981092839660402</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.4255422506051418</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.283665625099262</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.290792124295596</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>-0.2079298906652903</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
       <c r="U4" t="n">
-        <v>0.2079298906652903</v>
+        <v>0.05432768639273383</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5744577493948582</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.55789224952741</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
+        <v>0.05432768639273383</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3981092839660402</v>
       </c>
       <c r="Y4" t="n">
-        <v>45.95661995158865</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>45.95661995158865</v>
+        <v>2.75</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>31.84874271728322</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>31.84874271728322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Yk0Wxb5</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lorient</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>clermont</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -842,84 +888,96 @@
       <c r="F5" t="n">
         <v>551</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.2</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5848930481283423</v>
+        <v>4.33</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2256016042780749</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1895053475935829</v>
+        <v>0.1512839923135154</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0553791887125219</v>
+        <v>0.2183660397135038</v>
       </c>
       <c r="N5" t="n">
+        <v>0.6303499679729809</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05761354888375658</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1345400265066816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1746104668842328</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6908495066090855</v>
+      </c>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.4923772643437557</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2944436302719333</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.2131791053843112</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>-0.09251578378458664</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1</v>
-      </c>
       <c r="U5" t="n">
-        <v>0.09251578378458664</v>
+        <v>0.06049953863610458</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5076227356562444</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.282608695652174</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
+        <v>0.06049953863610458</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6908495066090855</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.60981885249955</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>40.60981885249955</v>
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>55.26796052872684</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>55.26796052872684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xObInbrn</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -928,84 +986,96 @@
       <c r="F6" t="n">
         <v>551</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.25</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I6" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7223026792179579</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1788559015206372</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09884141926140477</v>
+        <v>0.6297577854671281</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06497011760169658</v>
+        <v>0.2249134948096886</v>
       </c>
       <c r="N6" t="n">
+        <v>0.1453287197231834</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0586080586080584</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.6458454848983202</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.24062082636494</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.1135336887367399</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>0.5683378774600913</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2741924945433822</v>
+      </c>
       <c r="S6" t="n">
-        <v>-0.07645719431963771</v>
+        <v>0.1574696279965265</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07645719431963771</v>
+        <v>-0.06141990800703678</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3541545151016798</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>3.38135593220339</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
+        <v>-0.06141990800703678</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5683378774600913</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.33236120813439</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>28.33236120813439</v>
+        <v>1.5</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>45.46703019680731</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>45.46703019680731</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OKfEmvTu</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>metz</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1014,84 +1084,96 @@
       <c r="F7" t="n">
         <v>551</v>
       </c>
-      <c r="G7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.7</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2000772499034376</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2568559289300889</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5430668211664735</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05222515748831524</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N7" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.6573982211643515</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.06372951367054189</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.2788722651651065</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>0.4604288241086914</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2590050595417363</v>
+      </c>
       <c r="S7" t="n">
-        <v>0.4573209712609139</v>
+        <v>0.2805661163495721</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4573209712609139</v>
+        <v>0.000105394247841506</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6573982211643515</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>0.000105394247841506</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4604288241086914</v>
       </c>
       <c r="Y7" t="n">
-        <v>52.59185769314812</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>52.59185769314812</v>
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>36.83430592869531</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>36.83430592869531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tnl8UGSH</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1100,84 +1182,96 @@
       <c r="F8" t="n">
         <v>551</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6389405204460966</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1891263940520446</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1719330855018587</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05749385749385749</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6156360722259568</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P8" t="n">
-        <v>0.251132880122871</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.133231047651172</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>0.3644856693838699</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2301210490883976</v>
+      </c>
       <c r="S8" t="n">
-        <v>-0.02330444822013977</v>
+        <v>0.4053932815277326</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.02330444822013977</v>
+        <v>-0.0680984917812254</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6156360722259568</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>-0.0680984917812254</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4053932815277326</v>
       </c>
       <c r="Y8" t="n">
-        <v>49.25088577807655</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>49.25088577807655</v>
+        <v>2</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>32.43146252221861</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>32.43146252221861</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fVodXIra</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1186,77 +1280,87 @@
       <c r="F9" t="n">
         <v>551</v>
       </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.4</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3181818181818181</v>
-      </c>
       <c r="K9" t="n">
-        <v>0.2807486631016043</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4010695187165775</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N9" t="n">
+        <v>0.2973183054799844</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05106209150326801</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>0.234329403268049</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3367897036040899</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.428880893127861</v>
+        <v>0.3765281144980541</v>
       </c>
       <c r="R9" t="n">
+        <v>0.2334350222857216</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3900368632162244</v>
+      </c>
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
+        <v>0.09271855773623994</v>
+      </c>
+      <c r="V9" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.428880893127861</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>0.09271855773623994</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3900368632162244</v>
       </c>
       <c r="Y9" t="n">
-        <v>34.31047145022888</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>34.31047145022888</v>
+        <v>3.2</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>31.20294905729795</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>31.20294905729795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>C6diYbTh</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45431.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1265,7 +1369,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1274,65 +1378,77 @@
       <c r="F10" t="n">
         <v>551</v>
       </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.6</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3187066974595842</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2655889145496536</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.4157043879907621</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04589371980676349</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2634201695928</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3126713810085349</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4239084493986652</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>0.4279683296185534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2836033409632415</v>
+      </c>
       <c r="S10" t="n">
-        <v>0.00820406140790314</v>
+        <v>0.2884283294182053</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00820406140790314</v>
+        <v>-0.03235510024229654</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4239084493986652</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>-0.03235510024229654</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4279683296185534</v>
       </c>
       <c r="Y10" t="n">
-        <v>33.91267595189322</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>33.91267595189322</v>
+        <v>2.05</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>34.23746636948427</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>34.23746636948427</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/predicciones.xlsx
+++ b/p6_deployment/data/france/predicciones.xlsx
@@ -629,28 +629,28 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1746666286593137</v>
+        <v>0.1729686475272086</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1541996299822143</v>
+        <v>0.1505997669895271</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6711337413584719</v>
+        <v>0.6764315854832647</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09107254808973153</v>
+        <v>0.09637039221452426</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09107254808973153</v>
+        <v>0.09637039221452426</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6711337413584719</v>
+        <v>0.6764315854832647</v>
       </c>
       <c r="Y2" t="n">
         <v>1.62</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>53.69069930867775</v>
+        <v>54.11452683866117</v>
       </c>
       <c r="AB2" t="n">
-        <v>53.69069930867775</v>
+        <v>54.11452683866117</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2311760468323598</v>
+        <v>0.2317616976083876</v>
       </c>
       <c r="R3" t="n">
-        <v>0.188741386262389</v>
+        <v>0.1873067975146034</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5800825669052508</v>
+        <v>0.580931504877009</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1497866167494877</v>
+        <v>0.1506355547212458</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1497866167494877</v>
+        <v>0.1506355547212458</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5800825669052508</v>
+        <v>0.580931504877009</v>
       </c>
       <c r="Y3" t="n">
         <v>2.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>46.40660535242007</v>
+        <v>46.47452039016072</v>
       </c>
       <c r="AB3" t="n">
-        <v>46.40660535242007</v>
+        <v>46.47452039016072</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3528486016858882</v>
+        <v>0.3533679002749218</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2490421143480716</v>
+        <v>0.2489795619064891</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3981092839660402</v>
+        <v>0.3976525378185889</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05432768639273383</v>
+        <v>0.05387094024528255</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05432768639273383</v>
+        <v>0.05387094024528255</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3981092839660402</v>
+        <v>0.3976525378185889</v>
       </c>
       <c r="Y4" t="n">
         <v>2.75</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>31.84874271728322</v>
+        <v>31.81220302548711</v>
       </c>
       <c r="AB4" t="n">
-        <v>31.84874271728322</v>
+        <v>31.81220302548711</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1345400265066816</v>
+        <v>0.1308839083829359</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1746104668842328</v>
+        <v>0.1721410635214641</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6908495066090855</v>
+        <v>0.6969750280956001</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06049953863610458</v>
+        <v>0.06662506012261915</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06049953863610458</v>
+        <v>0.06662506012261915</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6908495066090855</v>
+        <v>0.6969750280956001</v>
       </c>
       <c r="Y5" t="n">
         <v>1.5</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>55.26796052872684</v>
+        <v>55.75800224764801</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.26796052872684</v>
+        <v>55.75800224764801</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5683378774600913</v>
+        <v>0.5670563869178281</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2741924945433822</v>
+        <v>0.2753010456706311</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1574696279965265</v>
+        <v>0.1576425674115408</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06141990800703678</v>
+        <v>-0.06270139854930001</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.06141990800703678</v>
+        <v>-0.06270139854930001</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5683378774600913</v>
+        <v>0.5670563869178281</v>
       </c>
       <c r="Y6" t="n">
         <v>1.5</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>45.46703019680731</v>
+        <v>45.36451095342625</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.46703019680731</v>
+        <v>45.36451095342625</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4604288241086914</v>
+        <v>0.456032217671363</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2590050595417363</v>
+        <v>0.2582018072471896</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2805661163495721</v>
+        <v>0.2857659750814475</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000105394247841506</v>
+        <v>-0.004291212189486859</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000105394247841506</v>
+        <v>-0.004291212189486859</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4604288241086914</v>
+        <v>0.456032217671363</v>
       </c>
       <c r="Y7" t="n">
         <v>2.05</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>36.83430592869531</v>
+        <v>36.48257741370904</v>
       </c>
       <c r="AB7" t="n">
-        <v>36.83430592869531</v>
+        <v>36.48257741370904</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3644856693838699</v>
+        <v>0.3661568152418682</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2301210490883976</v>
+        <v>0.2318042695397813</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4053932815277326</v>
+        <v>0.4020389152183506</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0680984917812254</v>
+        <v>-0.07145285809060742</v>
       </c>
       <c r="V8" t="n">
         <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0680984917812254</v>
+        <v>-0.07145285809060742</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4053932815277326</v>
+        <v>0.4020389152183506</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>32.43146252221861</v>
+        <v>32.16311321746804</v>
       </c>
       <c r="AB8" t="n">
-        <v>32.43146252221861</v>
+        <v>32.16311321746804</v>
       </c>
     </row>
     <row r="9">
@@ -1315,28 +1315,28 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3765281144980541</v>
+        <v>0.3787959845619371</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2334350222857216</v>
+        <v>0.2353448661406139</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3900368632162244</v>
+        <v>0.3858591492974488</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09271855773623994</v>
+        <v>0.08854084381746435</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09271855773623994</v>
+        <v>0.08854084381746435</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3900368632162244</v>
+        <v>0.3858591492974488</v>
       </c>
       <c r="Y9" t="n">
         <v>3.2</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>31.20294905729795</v>
+        <v>30.8687319437959</v>
       </c>
       <c r="AB9" t="n">
-        <v>31.20294905729795</v>
+        <v>30.8687319437959</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4279683296185534</v>
+        <v>0.4324341330827636</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2836033409632415</v>
+        <v>0.28390046926644</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2884283294182053</v>
+        <v>0.2836653976507963</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.03235510024229654</v>
+        <v>-0.02788929677808633</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03235510024229654</v>
+        <v>-0.02788929677808633</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4279683296185534</v>
+        <v>0.4324341330827636</v>
       </c>
       <c r="Y10" t="n">
         <v>2.05</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>34.23746636948427</v>
+        <v>34.59473064662109</v>
       </c>
       <c r="AB10" t="n">
-        <v>34.23746636948427</v>
+        <v>34.59473064662109</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/predicciones.xlsx
+++ b/p6_deployment/data/france/predicciones.xlsx
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>54.11452683866117</v>
+        <v>20.29294756449794</v>
       </c>
       <c r="AB2" t="n">
-        <v>54.11452683866117</v>
+        <v>20.29294756449794</v>
       </c>
     </row>
     <row r="3">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>46.47452039016072</v>
+        <v>17.42794514631027</v>
       </c>
       <c r="AB3" t="n">
-        <v>46.47452039016072</v>
+        <v>17.42794514631027</v>
       </c>
     </row>
     <row r="4">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.3677036001398113</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.2757777001048585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.3565186997553303</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.06650264668605077</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -837,19 +837,19 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05387094024528255</v>
+        <v>0.0411338380632586</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05387094024528255</v>
+        <v>0.0411338380632586</v>
       </c>
       <c r="X4" t="n">
         <v>0.3976525378185889</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>31.81220302548711</v>
+        <v>11.92957613455767</v>
       </c>
       <c r="AB4" t="n">
-        <v>31.81220302548711</v>
+        <v>11.92957613455767</v>
       </c>
     </row>
     <row r="5">
@@ -899,55 +899,55 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1512839923135154</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2183660397135038</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6303499679729809</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05761354888375658</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1308839083829359</v>
+        <v>0.1295641630952608</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1721410635214641</v>
+        <v>0.1728765496975989</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6969750280956001</v>
+        <v>0.6975592872071401</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06662506012261915</v>
+        <v>0.04369317407792372</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06662506012261915</v>
+        <v>0.04369317407792372</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6969750280956001</v>
+        <v>0.6975592872071401</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>55.75800224764801</v>
+        <v>20.9267786162142</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.75800224764801</v>
+        <v>20.9267786162142</v>
       </c>
     </row>
     <row r="6">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>45.36451095342625</v>
+        <v>17.01169160753484</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.36451095342625</v>
+        <v>17.01169160753484</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.456032217671363</v>
+        <v>0.4567094682001097</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2582018072471896</v>
+        <v>0.2582212984756653</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2857659750814475</v>
+        <v>0.2850692333242246</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.004291212189486859</v>
+        <v>-0.003613961660740239</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.004291212189486859</v>
+        <v>-0.003613961660740239</v>
       </c>
       <c r="X7" t="n">
-        <v>0.456032217671363</v>
+        <v>0.4567094682001097</v>
       </c>
       <c r="Y7" t="n">
         <v>2.05</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>36.48257741370904</v>
+        <v>13.70128404600329</v>
       </c>
       <c r="AB7" t="n">
-        <v>36.48257741370904</v>
+        <v>13.70128404600329</v>
       </c>
     </row>
     <row r="8">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>32.16311321746804</v>
+        <v>12.06116745655052</v>
       </c>
       <c r="AB8" t="n">
-        <v>32.16311321746804</v>
+        <v>12.06116745655052</v>
       </c>
     </row>
     <row r="9">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>30.8687319437959</v>
+        <v>11.57577447892346</v>
       </c>
       <c r="AB9" t="n">
-        <v>30.8687319437959</v>
+        <v>11.57577447892346</v>
       </c>
     </row>
     <row r="10">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>34.59473064662109</v>
+        <v>12.97302399248291</v>
       </c>
       <c r="AB10" t="n">
-        <v>34.59473064662109</v>
+        <v>12.97302399248291</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/predicciones.xlsx
+++ b/p6_deployment/data/france/predicciones.xlsx
@@ -629,28 +629,28 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1729686475272086</v>
+        <v>0.1664549248772655</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1505997669895271</v>
+        <v>0.1487827602374613</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="Y2" t="n">
         <v>1.62</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2317616976083876</v>
+        <v>0.2371626881820494</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1873067975146034</v>
+        <v>0.1955269582216931</v>
       </c>
       <c r="S3" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="X3" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="Y3" t="n">
         <v>2.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3533679002749218</v>
+        <v>0.354926915744822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2489795619064891</v>
+        <v>0.2495066794755585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="Y4" t="n">
         <v>2.63</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1295641630952608</v>
+        <v>0.1427096599821709</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1728765496975989</v>
+        <v>0.1812842175949421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="Y5" t="n">
         <v>1.45</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2753010456706311</v>
+        <v>0.275418703280472</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1576425674115408</v>
+        <v>0.1510256328109897</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="Y6" t="n">
         <v>1.5</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2582212984756653</v>
+        <v>0.260593877861823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2850692333242246</v>
+        <v>0.2846952181133715</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="Y7" t="n">
         <v>2.05</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3661568152418682</v>
+        <v>0.3483132254346947</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2318042695397813</v>
+        <v>0.2281432612817216</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="V8" t="n">
         <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
     </row>
     <row r="9">
@@ -1312,34 +1312,34 @@
         <v>0.05106209150326801</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3787959845619371</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2353448661406139</v>
+        <v>0.2369855400499945</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3793676215468028</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="R10" t="n">
-        <v>0.28390046926644</v>
+        <v>0.2827917961495244</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2836653976507963</v>
+        <v>0.2805224764028122</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="Y10" t="n">
         <v>2.05</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
     </row>
   </sheetData>
